--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Obj.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Obj.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Momiji</t>
+          <t>momiji</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Flor</t>
+          <t>flor</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Flor Azul</t>
+          <t>flor azul</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Flor Amarela</t>
+          <t>flor amarela</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Flor Branca</t>
+          <t>flor branca</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Erva Daninha</t>
+          <t>mato</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cogumelo</t>
+          <t>cogumelo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Erva Daninha</t>
+          <t>mato</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rafflesia</t>
+          <t>rafflesia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seixo</t>
+          <t>seixo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cristal</t>
+          <t>cristal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pedra</t>
+          <t>pedra</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Árvore de Cogumelos</t>
+          <t>árvore de cogumelo</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Árvore de Natal</t>
+          <t>árvore de natal</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Crim</t>
+          <t>crim</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Árvore de Cogumelos</t>
+          <t>árvore de cogumelo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cacto</t>
+          <t>cacto</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Árvore Palulu</t>
+          <t>árvore de palulu</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Minério</t>
+          <t>minério</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minério de Gemas</t>
+          <t>minério de gemas</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lírio-d'Água</t>
+          <t>nenúfar</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Suporte de Parede</t>
+          <t>suporte de parede</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telhado </t>
+          <t>telhado</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Janela</t>
+          <t>janela</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Moldura de Parede</t>
+          <t>moldura de madeira</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>wall frame</t>
+          <t>wooden frame</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Estrada</t>
+          <t>estrada</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Telhado 2</t>
+          <t>telhado2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Telhado 3</t>
+          <t>telhado3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Telhado 4</t>
+          <t>telhado4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Telhado 5</t>
+          <t>telhado5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Telhado 6</t>
+          <t>telhado6</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Trilho</t>
+          <t>trilho</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Abismo</t>
+          <t>abismo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estrada de Pedra</t>
+          <t>estrada de pedra</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Destroço</t>
+          <t>destroços</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Trigo</t>
+          <t>trigo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rabanete</t>
+          <t>rabanete</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Teste</t>
+          <t>teste</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Repolho</t>
+          <t>repolho</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tomate</t>
+          <t>tomate</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cenoura</t>
+          <t>cenoura</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Inhame</t>
+          <t>imo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Milho</t>
+          <t>milho</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estrada</t>
+          <t>estrada</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estrada Estreita</t>
+          <t>estrada estreita</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pedaço</t>
+          <t>pedaço</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Destroço</t>
+          <t>destroços</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Árvore de Cogumelos</t>
+          <t>árvore de cogumelo</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ninho de Pássaro</t>
+          <t>ninho de pássaro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Árvore de Maçã</t>
+          <t>macieira</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Baga</t>
+          <t>frutas silvestres</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Grande Pedra</t>
+          <t>rocha grande</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Osso</t>
+          <t>osso</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Roseira</t>
+          <t>árvore de pau-rosa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Abeto</t>
+          <t>abeto</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cedro</t>
+          <t>cedro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bétula</t>
+          <t>bétula</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pinheiro</t>
+          <t>pinheiro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Carvalho</t>
+          <t>carvalho</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Árvore Queimada</t>
+          <t>árvore queimada</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Musgo</t>
+          <t>musgo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Arbusto de Videira</t>
+          <t>arbusto de trepadeiras</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Árvore Fóssil Decomposta</t>
+          <t>árvore fóssil apodrecida</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Árvore Fóssil</t>
+          <t>árvore fóssil</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Grande Árvore Fóssil</t>
+          <t>árvore fóssil grande</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fóssil Decomposto</t>
+          <t>fóssil apodrecido</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bolardo</t>
+          <t>pilarete</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Telhado 7</t>
+          <t>telhado7</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Silhueta de Peixe</t>
+          <t>silhueta de peixe</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Árvore de Mogno</t>
+          <t>mogno</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Árvore de Acácia</t>
+          <t>acácia</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Piso Rachado</t>
+          <t>piso rachado</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Toco</t>
+          <t>toco</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alga</t>
+          <t>alga marinha</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Concha</t>
+          <t>concha</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Coral</t>
+          <t>coral</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salgueiro</t>
+          <t>salgueiro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cerejeira</t>
+          <t>cerejeira</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Uva</t>
+          <t>uva</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monte de Folhas Caídas</t>
+          <t>pilha de folhas caídas</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Algodão</t>
+          <t>algodão</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remanescente</t>
+          <t>resto</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Destroço</t>
+          <t>destroços</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Monte</t>
+          <t>monte</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Destroço</t>
+          <t>destroços</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Destroço</t>
+          <t>destroços</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Destroço</t>
+          <t>destroços</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Arroz</t>
+          <t>arroz</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Linha Branca</t>
+          <t>linha branca</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fruta Arco-Íris</t>
+          <t>fruta do arco-íris</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Rocha de Sal</t>
+          <t>rocha de sal</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Borda</t>
+          <t>divisa</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Estalagmite</t>
+          <t>estalagmite</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Árvore Decomposta</t>
+          <t>árvore apodrecida</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Parede Decomposta</t>
+          <t>parede apodrecida</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Parede Decomposta</t>
+          <t>parede apodrecida</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Trilho</t>
+          <t>trilho</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Trilho</t>
+          <t>trilho</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tanchagem</t>
+          <t>taboa</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Rocha Enorme</t>
+          <t>rocha colossal</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Moldura de Parede</t>
+          <t>moldura de madeira</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>wall frame</t>
+          <t>wooden frame</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rocha de Enxofre</t>
+          <t>rocha de enxofre</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bambu</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>api</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pasto</t>
+          <t>pasto</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3362,22 +3362,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Beta 22.24</t>
+          <t>EA 23.297</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Moldura de Parede</t>
+          <t>moldura de metal</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>wall frame</t>
+          <t>metal frame</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>枠</t>
+          <t>鉄枠</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Químicos</t>
+          <t>produtos químicos</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Grama Prateada</t>
+          <t>capim prateado</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Detritos</t>
+          <t>escombros</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Esteira Transportadora</t>
+          <t>esteira transportadora</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fragmentos</t>
+          <t>fragmentos</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bananeira</t>
+          <t>bananeira</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Laranjeira</t>
+          <t>laranjeira</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Pereira</t>
+          <t>pereira</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Grama Vermelha</t>
+          <t>grama vermelha</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Grama Azul</t>
+          <t>grama azul</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Grama Roxa</t>
+          <t>grama roxa</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Árvore de Feywood</t>
+          <t>árvore feérica</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Árvore de Madeira de Coral</t>
+          <t>árvore de coral</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Flor Branca</t>
+          <t>flor branca</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Samambaia</t>
+          <t>samambaia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Café</t>
+          <t>café</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tabaco</t>
+          <t>tabaco</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Telhado 8</t>
+          <t>telhado8</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Telhado 9</t>
+          <t>telhado9</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Telhado 10</t>
+          <t>telhado10</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Grama Verde</t>
+          <t>grama verde</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Telhado 11</t>
+          <t>telhado11</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Telhado 12</t>
+          <t>telhado12</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Telhado 13</t>
+          <t>telhado13</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Telhado 14</t>
+          <t>telhado14</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Telhado 15</t>
+          <t>telhado15</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Telhado 16</t>
+          <t>telhado16</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Telhado 17</t>
+          <t>telhado17</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Linha Neon</t>
+          <t>linha de neon</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Recife De Coral</t>
+          <t>recife de coral</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Alga Marinha Profunda</t>
+          <t>alga profunda</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cabocchi</t>
+          <t>cabocchi</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Girassol</t>
+          <t>girassol</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Túlipa</t>
+          <t>tulipa</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Pimenta Vermelha</t>
+          <t>pimenta</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Osso</t>
+          <t>osso</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4377,6 +4377,249 @@
       <c r="E146" t="inlineStr">
         <is>
           <t>竜骨</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EA 23.283</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>pedra de passagem</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>stepping stone</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>踏み石</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>EA 23.297</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ovo</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>egg</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>卵</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>EA 23.308</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>rosa</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>rose</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>バラ</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EA 23.322</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>hortênsia</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>hydrangea</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>アジサイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>EA 23.327</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>chá</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>tea</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>茶</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>EA 23.332</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>imo doce</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>sweet imo</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>サツマイーモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>EA 23.341</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>campo de flores</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>flower field</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>花畑</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>EA 23.341</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>campo de flores</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>flower field</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>花畑</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>EA 23.347</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>mato</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>weed</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>雑草</t>
         </is>
       </c>
     </row>
